--- a/call-delivery/intake/2026-07/Repo.xlsx
+++ b/call-delivery/intake/2026-07/Repo.xlsx
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +53,19 @@
     </font>
     <font>
       <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5AAC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -122,7 +134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,7 +143,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +156,26 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I143"/>
+  <dimension ref="B2:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -539,12 +571,21 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>CALL DELIVERY  —  Outbound Dialing Schedule (Intake)</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>GROUP STRATEGY &amp; NOTES  (carried over from July 2026 master)</t>
         </is>
       </c>
     </row>
@@ -555,6 +596,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>General Strategy</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -576,6 +624,11 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>M-F (2) Full Passes</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
@@ -593,8 +646,27 @@
           <t>Submitted Date:</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="17" t="n">
         <v>46220</v>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     1st generally 7:30, 8 &amp; 10 but vary for effectiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     2nd generally 2 or 3p</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>Auto Messages each day on all 1st passes</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -638,13 +710,18 @@
           <t>Special Instructions</t>
         </is>
       </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>Beginning on 5th, add Repo RP pass, with AMs, 1 hour after Repo completes 1st pass</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D10" s="10" t="n">
@@ -669,13 +746,18 @@
           <t>AM Daily</t>
         </is>
       </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>NO REPO Last Day of Month</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D11" s="10" t="n">
@@ -702,7 +784,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D12" s="10" t="n">
@@ -723,13 +805,18 @@
         </is>
       </c>
       <c r="I12" s="12" t="n"/>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D13" s="10" t="n">
@@ -750,13 +837,28 @@
         </is>
       </c>
       <c r="I13" s="12" t="n"/>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>List #</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>List Specific Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D14" s="10" t="n">
@@ -781,13 +883,26 @@
           <t>AM Daily</t>
         </is>
       </c>
+      <c r="K14" s="20" t="n">
+        <v>19100</v>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>Repo</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>All Repo Passes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D15" s="10" t="n">
@@ -808,13 +923,26 @@
         </is>
       </c>
       <c r="I15" s="12" t="n"/>
+      <c r="K15" s="20" t="n">
+        <v>9014</v>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>ALL_REPO_PR</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>See General Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D16" s="10" t="n">
@@ -841,7 +969,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D17" s="10" t="n">
@@ -868,7 +996,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D18" s="10" t="n">
@@ -899,7 +1027,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D19" s="10" t="n">
@@ -926,7 +1054,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D20" s="10" t="n">
@@ -953,7 +1081,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D21" s="10" t="n">
@@ -980,7 +1108,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D22" s="10" t="n">
@@ -1011,7 +1139,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D23" s="10" t="n">
@@ -1038,7 +1166,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D24" s="10" t="n">
@@ -1065,7 +1193,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D25" s="10" t="n">
@@ -1096,7 +1224,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D26" s="10" t="n">
@@ -1123,7 +1251,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D27" s="10" t="n">
@@ -1150,7 +1278,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D28" s="10" t="n">
@@ -1177,7 +1305,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D29" s="10" t="n">
@@ -1208,7 +1336,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D30" s="10" t="n">
@@ -1235,7 +1363,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D31" s="10" t="n">
@@ -1262,7 +1390,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D32" s="10" t="n">
@@ -1293,7 +1421,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D33" s="10" t="n">
@@ -1320,7 +1448,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D34" s="10" t="n">
@@ -1347,7 +1475,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D35" s="10" t="n">
@@ -1374,7 +1502,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D36" s="10" t="n">
@@ -1405,7 +1533,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D37" s="10" t="n">
@@ -1432,7 +1560,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D38" s="10" t="n">
@@ -1459,7 +1587,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D39" s="10" t="n">
@@ -1490,7 +1618,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D40" s="10" t="n">
@@ -1517,7 +1645,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D41" s="10" t="n">
@@ -1544,7 +1672,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D42" s="10" t="n">
@@ -1571,7 +1699,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D43" s="10" t="n">
@@ -1602,7 +1730,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D44" s="10" t="n">
@@ -1629,7 +1757,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D45" s="10" t="n">
@@ -1656,7 +1784,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D46" s="10" t="n">
@@ -1683,7 +1811,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D47" s="10" t="n">
@@ -1714,7 +1842,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D48" s="10" t="n">
@@ -1741,7 +1869,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D49" s="10" t="n">
@@ -1768,7 +1896,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D50" s="10" t="n">
@@ -1799,7 +1927,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D51" s="10" t="n">
@@ -1826,7 +1954,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D52" s="10" t="n">
@@ -1853,7 +1981,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D53" s="10" t="n">
@@ -1880,7 +2008,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="C54" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D54" s="10" t="n">
@@ -1911,7 +2039,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D55" s="10" t="n">
@@ -1938,7 +2066,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D56" s="10" t="n">
@@ -1965,7 +2093,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D57" s="10" t="n">
@@ -1996,7 +2124,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D58" s="10" t="n">
@@ -2023,7 +2151,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="C59" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D59" s="10" t="n">
@@ -2050,7 +2178,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C60" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D60" s="10" t="n">
@@ -2077,7 +2205,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C61" s="9" t="n">
+      <c r="C61" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D61" s="10" t="n">
@@ -2108,7 +2236,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C62" s="9" t="n">
+      <c r="C62" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D62" s="10" t="n">
@@ -2135,7 +2263,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="C63" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D63" s="10" t="n">
@@ -2162,7 +2290,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="C64" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D64" s="10" t="n">
@@ -2189,7 +2317,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D65" s="10" t="n">
@@ -2220,7 +2348,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C66" s="9" t="n">
+      <c r="C66" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D66" s="10" t="n">
@@ -2247,7 +2375,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C67" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D67" s="10" t="n">
@@ -2274,7 +2402,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C68" s="9" t="n">
+      <c r="C68" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D68" s="10" t="n">
@@ -2305,7 +2433,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C69" s="9" t="n">
+      <c r="C69" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D69" s="10" t="n">
@@ -2332,7 +2460,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C70" s="9" t="n">
+      <c r="C70" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D70" s="10" t="n">
@@ -2359,7 +2487,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C71" s="9" t="n">
+      <c r="C71" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D71" s="10" t="n">
@@ -2386,7 +2514,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C72" s="9" t="n">
+      <c r="C72" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D72" s="10" t="n">
@@ -2417,7 +2545,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C73" s="9" t="n">
+      <c r="C73" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D73" s="10" t="n">
@@ -2444,7 +2572,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C74" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D74" s="10" t="n">
@@ -2471,7 +2599,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C75" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D75" s="10" t="n">
@@ -2502,7 +2630,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C76" s="9" t="n">
+      <c r="C76" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D76" s="10" t="n">
@@ -2529,7 +2657,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="C77" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D77" s="10" t="n">
@@ -2556,7 +2684,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="C78" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D78" s="10" t="n">
@@ -2583,7 +2711,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="n">
+      <c r="C79" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D79" s="10" t="n">
@@ -2614,7 +2742,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C80" s="9" t="n">
+      <c r="C80" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D80" s="10" t="n">
@@ -2641,7 +2769,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C81" s="9" t="n">
+      <c r="C81" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D81" s="10" t="n">
@@ -2668,7 +2796,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C82" s="9" t="n">
+      <c r="C82" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D82" s="10" t="n">
@@ -2695,7 +2823,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C83" s="9" t="n">
+      <c r="C83" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D83" s="10" t="n">
@@ -2726,7 +2854,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C84" s="9" t="n">
+      <c r="C84" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D84" s="10" t="n">
@@ -2753,7 +2881,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C85" s="9" t="n">
+      <c r="C85" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D85" s="10" t="n">
@@ -2780,7 +2908,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C86" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D86" s="10" t="n">
@@ -2811,7 +2939,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C87" s="9" t="n">
+      <c r="C87" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D87" s="10" t="n">
@@ -2838,7 +2966,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C88" s="9" t="n">
+      <c r="C88" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D88" s="10" t="n">
@@ -2865,7 +2993,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C89" s="9" t="n">
+      <c r="C89" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D89" s="10" t="n">
@@ -2892,7 +3020,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C90" s="9" t="n">
+      <c r="C90" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D90" s="10" t="n">
@@ -2923,7 +3051,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C91" s="9" t="n">
+      <c r="C91" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D91" s="10" t="n">
@@ -2950,7 +3078,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C92" s="9" t="n">
+      <c r="C92" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D92" s="10" t="n">
@@ -2977,7 +3105,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C93" s="9" t="n">
+      <c r="C93" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D93" s="10" t="n">
@@ -3004,7 +3132,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C94" s="9" t="n"/>
+      <c r="C94" s="18" t="n"/>
       <c r="D94" s="10" t="n"/>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
@@ -3017,7 +3145,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C95" s="9" t="n"/>
+      <c r="C95" s="18" t="n"/>
       <c r="D95" s="10" t="n"/>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
@@ -3030,7 +3158,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C96" s="9" t="n"/>
+      <c r="C96" s="18" t="n"/>
       <c r="D96" s="10" t="n"/>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
@@ -3043,7 +3171,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C97" s="9" t="n"/>
+      <c r="C97" s="18" t="n"/>
       <c r="D97" s="10" t="n"/>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
@@ -3056,7 +3184,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C98" s="9" t="n"/>
+      <c r="C98" s="18" t="n"/>
       <c r="D98" s="10" t="n"/>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
@@ -3069,7 +3197,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C99" s="9" t="n"/>
+      <c r="C99" s="18" t="n"/>
       <c r="D99" s="10" t="n"/>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
@@ -3082,7 +3210,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C100" s="9" t="n"/>
+      <c r="C100" s="18" t="n"/>
       <c r="D100" s="10" t="n"/>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
@@ -3095,7 +3223,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C101" s="9" t="n"/>
+      <c r="C101" s="18" t="n"/>
       <c r="D101" s="10" t="n"/>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
@@ -3108,7 +3236,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C102" s="9" t="n"/>
+      <c r="C102" s="18" t="n"/>
       <c r="D102" s="10" t="n"/>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
@@ -3121,7 +3249,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C103" s="9" t="n"/>
+      <c r="C103" s="18" t="n"/>
       <c r="D103" s="10" t="n"/>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
@@ -3134,7 +3262,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C104" s="9" t="n"/>
+      <c r="C104" s="18" t="n"/>
       <c r="D104" s="10" t="n"/>
       <c r="E104" s="11" t="n"/>
       <c r="F104" s="11" t="n"/>
@@ -3147,7 +3275,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C105" s="9" t="n"/>
+      <c r="C105" s="18" t="n"/>
       <c r="D105" s="10" t="n"/>
       <c r="E105" s="11" t="n"/>
       <c r="F105" s="11" t="n"/>
@@ -3160,7 +3288,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C106" s="9" t="n"/>
+      <c r="C106" s="18" t="n"/>
       <c r="D106" s="10" t="n"/>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
@@ -3173,7 +3301,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C107" s="9" t="n"/>
+      <c r="C107" s="18" t="n"/>
       <c r="D107" s="10" t="n"/>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
@@ -3186,7 +3314,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C108" s="9" t="n"/>
+      <c r="C108" s="18" t="n"/>
       <c r="D108" s="10" t="n"/>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
@@ -3199,7 +3327,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C109" s="9" t="n"/>
+      <c r="C109" s="18" t="n"/>
       <c r="D109" s="10" t="n"/>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
@@ -3212,7 +3340,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C110" s="9" t="n"/>
+      <c r="C110" s="18" t="n"/>
       <c r="D110" s="10" t="n"/>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
@@ -3225,7 +3353,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C111" s="9" t="n"/>
+      <c r="C111" s="18" t="n"/>
       <c r="D111" s="10" t="n"/>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
@@ -3238,7 +3366,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C112" s="9" t="n"/>
+      <c r="C112" s="18" t="n"/>
       <c r="D112" s="10" t="n"/>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
@@ -3251,7 +3379,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C113" s="9" t="n"/>
+      <c r="C113" s="18" t="n"/>
       <c r="D113" s="10" t="n"/>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
@@ -3264,7 +3392,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C114" s="9" t="n"/>
+      <c r="C114" s="18" t="n"/>
       <c r="D114" s="10" t="n"/>
       <c r="E114" s="11" t="n"/>
       <c r="F114" s="11" t="n"/>
@@ -3277,7 +3405,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C115" s="9" t="n"/>
+      <c r="C115" s="18" t="n"/>
       <c r="D115" s="10" t="n"/>
       <c r="E115" s="11" t="n"/>
       <c r="F115" s="11" t="n"/>
@@ -3290,7 +3418,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C116" s="9" t="n"/>
+      <c r="C116" s="18" t="n"/>
       <c r="D116" s="10" t="n"/>
       <c r="E116" s="11" t="n"/>
       <c r="F116" s="11" t="n"/>
@@ -3303,7 +3431,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C117" s="9" t="n"/>
+      <c r="C117" s="18" t="n"/>
       <c r="D117" s="10" t="n"/>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
@@ -3316,7 +3444,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C118" s="9" t="n"/>
+      <c r="C118" s="18" t="n"/>
       <c r="D118" s="10" t="n"/>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
@@ -3329,7 +3457,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C119" s="9" t="n"/>
+      <c r="C119" s="18" t="n"/>
       <c r="D119" s="10" t="n"/>
       <c r="E119" s="11" t="n"/>
       <c r="F119" s="11" t="n"/>
@@ -3342,7 +3470,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C120" s="9" t="n"/>
+      <c r="C120" s="18" t="n"/>
       <c r="D120" s="10" t="n"/>
       <c r="E120" s="11" t="n"/>
       <c r="F120" s="11" t="n"/>
@@ -3355,7 +3483,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C121" s="9" t="n"/>
+      <c r="C121" s="18" t="n"/>
       <c r="D121" s="10" t="n"/>
       <c r="E121" s="11" t="n"/>
       <c r="F121" s="11" t="n"/>
@@ -3368,7 +3496,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C122" s="9" t="n"/>
+      <c r="C122" s="18" t="n"/>
       <c r="D122" s="10" t="n"/>
       <c r="E122" s="11" t="n"/>
       <c r="F122" s="11" t="n"/>
@@ -3381,7 +3509,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C123" s="9" t="n"/>
+      <c r="C123" s="18" t="n"/>
       <c r="D123" s="10" t="n"/>
       <c r="E123" s="11" t="n"/>
       <c r="F123" s="11" t="n"/>
@@ -3394,7 +3522,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C124" s="9" t="n"/>
+      <c r="C124" s="18" t="n"/>
       <c r="D124" s="10" t="n"/>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
@@ -3407,7 +3535,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C125" s="9" t="n"/>
+      <c r="C125" s="18" t="n"/>
       <c r="D125" s="10" t="n"/>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="11" t="n"/>
@@ -3420,7 +3548,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C126" s="9" t="n"/>
+      <c r="C126" s="18" t="n"/>
       <c r="D126" s="10" t="n"/>
       <c r="E126" s="11" t="n"/>
       <c r="F126" s="11" t="n"/>
@@ -3433,7 +3561,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C127" s="9" t="n"/>
+      <c r="C127" s="18" t="n"/>
       <c r="D127" s="10" t="n"/>
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="11" t="n"/>
@@ -3446,7 +3574,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C128" s="9" t="n"/>
+      <c r="C128" s="18" t="n"/>
       <c r="D128" s="10" t="n"/>
       <c r="E128" s="11" t="n"/>
       <c r="F128" s="11" t="n"/>
@@ -3459,7 +3587,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C129" s="9" t="n"/>
+      <c r="C129" s="18" t="n"/>
       <c r="D129" s="10" t="n"/>
       <c r="E129" s="11" t="n"/>
       <c r="F129" s="11" t="n"/>
@@ -3472,7 +3600,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C130" s="9" t="n"/>
+      <c r="C130" s="18" t="n"/>
       <c r="D130" s="10" t="n"/>
       <c r="E130" s="11" t="n"/>
       <c r="F130" s="11" t="n"/>
@@ -3485,7 +3613,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C131" s="9" t="n"/>
+      <c r="C131" s="18" t="n"/>
       <c r="D131" s="10" t="n"/>
       <c r="E131" s="11" t="n"/>
       <c r="F131" s="11" t="n"/>
@@ -3498,7 +3626,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C132" s="9" t="n"/>
+      <c r="C132" s="18" t="n"/>
       <c r="D132" s="10" t="n"/>
       <c r="E132" s="11" t="n"/>
       <c r="F132" s="11" t="n"/>
@@ -3511,7 +3639,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C133" s="9" t="n"/>
+      <c r="C133" s="18" t="n"/>
       <c r="D133" s="10" t="n"/>
       <c r="E133" s="11" t="n"/>
       <c r="F133" s="11" t="n"/>
@@ -3524,7 +3652,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C134" s="9" t="n"/>
+      <c r="C134" s="18" t="n"/>
       <c r="D134" s="10" t="n"/>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
@@ -3537,7 +3665,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C135" s="9" t="n"/>
+      <c r="C135" s="18" t="n"/>
       <c r="D135" s="10" t="n"/>
       <c r="E135" s="11" t="n"/>
       <c r="F135" s="11" t="n"/>
@@ -3550,7 +3678,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C136" s="9" t="n"/>
+      <c r="C136" s="18" t="n"/>
       <c r="D136" s="10" t="n"/>
       <c r="E136" s="11" t="n"/>
       <c r="F136" s="11" t="n"/>
@@ -3563,7 +3691,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C137" s="9" t="n"/>
+      <c r="C137" s="18" t="n"/>
       <c r="D137" s="10" t="n"/>
       <c r="E137" s="11" t="n"/>
       <c r="F137" s="11" t="n"/>
@@ -3576,7 +3704,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C138" s="9" t="n"/>
+      <c r="C138" s="18" t="n"/>
       <c r="D138" s="10" t="n"/>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
@@ -3589,7 +3717,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C139" s="9" t="n"/>
+      <c r="C139" s="18" t="n"/>
       <c r="D139" s="10" t="n"/>
       <c r="E139" s="11" t="n"/>
       <c r="F139" s="11" t="n"/>
@@ -3602,7 +3730,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C140" s="9" t="n"/>
+      <c r="C140" s="18" t="n"/>
       <c r="D140" s="10" t="n"/>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
@@ -3615,7 +3743,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C141" s="9" t="n"/>
+      <c r="C141" s="18" t="n"/>
       <c r="D141" s="10" t="n"/>
       <c r="E141" s="11" t="n"/>
       <c r="F141" s="11" t="n"/>
@@ -3628,7 +3756,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C142" s="9" t="n"/>
+      <c r="C142" s="18" t="n"/>
       <c r="D142" s="10" t="n"/>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
@@ -3641,7 +3769,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C143" s="9" t="n"/>
+      <c r="C143" s="18" t="n"/>
       <c r="D143" s="10" t="n"/>
       <c r="E143" s="11" t="n"/>
       <c r="F143" s="11" t="n"/>
@@ -3650,9 +3778,17 @@
       <c r="I143" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="10">
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K5:N5"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/call-delivery/intake/2026-07/Repo.xlsx
+++ b/call-delivery/intake/2026-07/Repo.xlsx
@@ -253,8 +253,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblSchedule" displayName="tblSchedule" ref="B9:I143" headerRowCount="1">
-  <autoFilter ref="B9:I143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblSchedule" displayName="tblSchedule" ref="B9:I139" headerRowCount="1">
+  <autoFilter ref="B9:I139"/>
   <tableColumns count="8">
     <tableColumn id="2" name="Business Group"/>
     <tableColumn id="3" name="Date"/>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N143"/>
+  <dimension ref="B2:N139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3020,57 +3020,25 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C90" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D90" s="10" t="n">
-        <v>0.34375</v>
-      </c>
+      <c r="C90" s="18" t="n"/>
+      <c r="D90" s="10" t="n"/>
       <c r="E90" s="11" t="n"/>
-      <c r="F90" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="11" t="inlineStr">
-        <is>
-          <t>Repo</t>
-        </is>
-      </c>
-      <c r="I90" s="12" t="inlineStr">
-        <is>
-          <t>AM Daily</t>
-        </is>
-      </c>
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="11" t="n"/>
+      <c r="I90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C91" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D91" s="10" t="n">
-        <v>0.4166666666666667</v>
-      </c>
+      <c r="C91" s="18" t="n"/>
+      <c r="D91" s="10" t="n"/>
       <c r="E91" s="11" t="n"/>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>Repo</t>
-        </is>
-      </c>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="11" t="n"/>
       <c r="I91" s="12" t="n"/>
     </row>
     <row r="92">
@@ -3078,26 +3046,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C92" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D92" s="10" t="n">
-        <v>0.5416666666666666</v>
-      </c>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="10" t="n"/>
       <c r="E92" s="11" t="n"/>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H92" s="11" t="inlineStr">
-        <is>
-          <t>RP</t>
-        </is>
-      </c>
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="11" t="n"/>
       <c r="I92" s="12" t="n"/>
     </row>
     <row r="93">
@@ -3105,26 +3059,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C93" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D93" s="10" t="n">
-        <v>0.5833333333333334</v>
-      </c>
+      <c r="C93" s="18" t="n"/>
+      <c r="D93" s="10" t="n"/>
       <c r="E93" s="11" t="n"/>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>Repo</t>
-        </is>
-      </c>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="11" t="n"/>
       <c r="I93" s="12" t="n"/>
     </row>
     <row r="94">
@@ -3724,58 +3664,6 @@
       <c r="G139" s="11" t="n"/>
       <c r="H139" s="11" t="n"/>
       <c r="I139" s="12" t="n"/>
-    </row>
-    <row r="140">
-      <c r="B140" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="10" t="n"/>
-      <c r="E140" s="11" t="n"/>
-      <c r="F140" s="11" t="n"/>
-      <c r="G140" s="11" t="n"/>
-      <c r="H140" s="11" t="n"/>
-      <c r="I140" s="12" t="n"/>
-    </row>
-    <row r="141">
-      <c r="B141" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C141" s="18" t="n"/>
-      <c r="D141" s="10" t="n"/>
-      <c r="E141" s="11" t="n"/>
-      <c r="F141" s="11" t="n"/>
-      <c r="G141" s="11" t="n"/>
-      <c r="H141" s="11" t="n"/>
-      <c r="I141" s="12" t="n"/>
-    </row>
-    <row r="142">
-      <c r="B142" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C142" s="18" t="n"/>
-      <c r="D142" s="10" t="n"/>
-      <c r="E142" s="11" t="n"/>
-      <c r="F142" s="11" t="n"/>
-      <c r="G142" s="11" t="n"/>
-      <c r="H142" s="11" t="n"/>
-      <c r="I142" s="12" t="n"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="8">
-        <f>IF($C$5="","",$C$5)</f>
-        <v/>
-      </c>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="10" t="n"/>
-      <c r="E143" s="11" t="n"/>
-      <c r="F143" s="11" t="n"/>
-      <c r="G143" s="11" t="n"/>
-      <c r="H143" s="11" t="n"/>
-      <c r="I143" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3794,23 +3682,23 @@
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Lists!$A$2:$A$21</formula1>
     </dataValidation>
-    <dataValidation sqref="E10:E143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E10:E139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$B$2:$B$12</formula1>
     </dataValidation>
-    <dataValidation sqref="F10:F143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F10:F139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$D$2:$D$31</formula1>
     </dataValidation>
-    <dataValidation sqref="H10:H143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H10:H139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$C$2:$C$15</formula1>
     </dataValidation>
-    <dataValidation sqref="G10:G143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="G10:G139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="C10:C143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThanOrEqual">
+    <dataValidation sqref="C10:C139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThanOrEqual">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D10:D143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="time" operator="between">
+    <dataValidation sqref="D10:D139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="time" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
